--- a/SampleData/Users.xlsx
+++ b/SampleData/Users.xlsx
@@ -8,8 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Users" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UserModulePermissions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'UserModulePermissions'!$A$1:$C$65</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +38,13 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +61,21 @@
         <fgColor rgb="00F0F7F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF4FB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -66,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -76,6 +99,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2037,4 +2069,1129 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Username</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>ModuleName</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>PermissionLevel</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>mgarcia</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>EditAndVoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>mgarcia</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>EditAndVoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>mgarcia</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>EodSales</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>EditAndVoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>mgarcia</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>EditAndVoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>dlee</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>EditAndVoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>dlee</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>EditAndVoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>dlee</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>EodSales</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>EditAndVoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>dlee</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>EditAndVoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ejackson</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>EditAndVoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>ejackson</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>EditAndVoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>ejackson</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>EodSales</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>EditAndVoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>ejackson</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>EditAndVoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>rjohnson</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>EditAndVoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>rjohnson</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>EditAndVoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>rjohnson</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>EodSales</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>ReadWrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>rjohnson</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>lmartinez</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>lmartinez</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>ReadWrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>lmartinez</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>EodSales</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>EditAndVoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>lmartinez</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>EditAndVoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>aanderso</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>ReadWrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>aanderso</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>aanderso</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>EodSales</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>EditAndVoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>aanderso</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>tmartin</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>ReadWrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>tmartin</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>EditAndVoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>tmartin</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>EodSales</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>ReadWrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>tmartin</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>btaylor</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>ReadWrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>btaylor</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>btaylor</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>EodSales</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>ReadWrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>btaylor</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>nwhite</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>nwhite</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>ReadWrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>nwhite</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>EodSales</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>nwhite</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>ReadWrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>gthompso</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>gthompso</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>gthompso</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>EodSales</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>ReadWrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>gthompso</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>jclark</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>ReadWrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>jclark</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>ReadWrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>jclark</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>EodSales</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>jclark</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>mlewis</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>mlewis</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>mlewis</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>EodSales</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>mlewis</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>ReadWrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>awalker</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>awalker</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>ReadWrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>awalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>EodSales</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>ReadWrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>awalker</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>chall</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>ReadWrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>chall</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>chall</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>EodSales</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>ReadWrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>chall</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>bking</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>bking</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>bking</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>EodSales</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>bking</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>lwright</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>lwright</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>lwright</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>EodSales</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>lwright</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C65"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>